--- a/ROSA_vitaSPEC/Results/test_pretraitements/total.beta.carotenes/Resultats_total.beta.carotenes_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/total.beta.carotenes/Resultats_total.beta.carotenes_moy_ADJR2.xlsx
@@ -19,11 +19,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Pretraitement</t>
   </si>
   <si>
+    <t>LV0_ADJR2</t>
+  </si>
+  <si>
     <t>LV1_ADJR2</t>
   </si>
   <si>
@@ -133,18 +136,6 @@
   </si>
   <si>
     <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
   </si>
   <si>
     <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
@@ -211,7 +202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,13 +218,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -243,7 +227,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -251,58 +235,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9C0006"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9C0006"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9C0006"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9C0006"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -602,15 +594,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -659,2309 +652,2238 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>0.37230667901446901</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C2">
-        <v>0.52657133098999753</v>
+        <v>0.37338043894805129</v>
       </c>
       <c r="D2">
-        <v>0.55728792299502228</v>
+        <v>0.52861610992937891</v>
       </c>
       <c r="E2">
-        <v>0.58855398658687341</v>
+        <v>0.56093096524535857</v>
       </c>
       <c r="F2">
-        <v>0.58677367360832922</v>
+        <v>0.59032362644636216</v>
       </c>
       <c r="G2">
-        <v>0.60004333134230692</v>
+        <v>0.58624440948527701</v>
       </c>
       <c r="H2">
-        <v>0.60363410749864188</v>
+        <v>0.60092773776743702</v>
       </c>
       <c r="I2">
-        <v>0.60493777517761471</v>
+        <v>0.60799936276694933</v>
       </c>
       <c r="J2">
-        <v>0.61689816330640945</v>
+        <v>0.61079324681865788</v>
       </c>
       <c r="K2">
-        <v>0.61002880480826993</v>
+        <v>0.61822769405321998</v>
       </c>
       <c r="L2">
-        <v>0.58932384089173795</v>
+        <v>0.61120705241978757</v>
       </c>
       <c r="M2">
-        <v>0.56103383412762708</v>
+        <v>0.58987002800774169</v>
       </c>
       <c r="N2">
-        <v>0.51790419737569737</v>
+        <v>0.5596476331292447</v>
       </c>
       <c r="O2">
-        <v>0.46940062107363112</v>
+        <v>0.51185665665739377</v>
       </c>
       <c r="P2">
-        <v>0.49193145025652069</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.46331588863555961</v>
+      </c>
+      <c r="Q2">
+        <v>0.48357028805246188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>0.46061837288201818</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C3">
-        <v>0.54045504300921432</v>
+        <v>0.46482521768253421</v>
       </c>
       <c r="D3">
-        <v>0.53691007568270155</v>
+        <v>0.5428590483604937</v>
       </c>
       <c r="E3">
-        <v>0.54280692265220842</v>
+        <v>0.53861837237658972</v>
       </c>
       <c r="F3">
-        <v>0.55346222030276448</v>
+        <v>0.54697477658628091</v>
       </c>
       <c r="G3">
-        <v>0.56741811962146715</v>
+        <v>0.55648648796821687</v>
       </c>
       <c r="H3">
-        <v>0.546755349188489</v>
+        <v>0.57020293693677271</v>
       </c>
       <c r="I3">
-        <v>0.54632357178736113</v>
+        <v>0.54918054959873808</v>
       </c>
       <c r="J3">
-        <v>0.53355917593117597</v>
+        <v>0.54684696801502097</v>
       </c>
       <c r="K3">
-        <v>0.51972071165770206</v>
+        <v>0.53177015959628338</v>
       </c>
       <c r="L3">
-        <v>0.48744629195374523</v>
+        <v>0.51636952805411496</v>
       </c>
       <c r="M3">
-        <v>0.42863837935150362</v>
+        <v>0.48153321898581752</v>
       </c>
       <c r="N3">
-        <v>0.35289721481101521</v>
+        <v>0.42428866757615502</v>
       </c>
       <c r="O3">
-        <v>0.31020262992119468</v>
+        <v>0.34700251064328452</v>
       </c>
       <c r="P3">
-        <v>0.27157908562472483</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.30088843453022091</v>
+      </c>
+      <c r="Q3">
+        <v>0.25692815663799862</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>0.38931600635720692</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C4">
-        <v>0.51447962548958504</v>
+        <v>0.39002657522288658</v>
       </c>
       <c r="D4">
-        <v>0.52676072764570736</v>
+        <v>0.51254407518627421</v>
       </c>
       <c r="E4">
-        <v>0.53128376522623144</v>
+        <v>0.52616965814244765</v>
       </c>
       <c r="F4">
-        <v>0.56704900611739728</v>
+        <v>0.53338038493331663</v>
       </c>
       <c r="G4">
-        <v>0.60928281530435069</v>
+        <v>0.57107479913015569</v>
       </c>
       <c r="H4">
-        <v>0.62504956281153523</v>
+        <v>0.61458118055471511</v>
       </c>
       <c r="I4">
-        <v>0.60689737291436563</v>
+        <v>0.62881121590756306</v>
       </c>
       <c r="J4">
-        <v>0.56928808073878268</v>
+        <v>0.61107095240741793</v>
       </c>
       <c r="K4">
-        <v>0.54523723614777408</v>
+        <v>0.57368994726133415</v>
       </c>
       <c r="L4">
-        <v>0.47349356615532051</v>
+        <v>0.55027569239866403</v>
       </c>
       <c r="M4">
-        <v>0.47348866354883251</v>
+        <v>0.48153080222813238</v>
       </c>
       <c r="N4">
-        <v>0.48302293337422991</v>
+        <v>0.47204373286903117</v>
       </c>
       <c r="O4">
-        <v>0.5040931442633183</v>
+        <v>0.48311596082752711</v>
       </c>
       <c r="P4">
-        <v>0.51870092591784644</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.50324270520951797</v>
+      </c>
+      <c r="Q4">
+        <v>0.51881510353403526</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>0.53471076293839759</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C5">
-        <v>0.53903580747291413</v>
+        <v>0.537105783013063</v>
       </c>
       <c r="D5">
-        <v>0.54853680141830319</v>
+        <v>0.5426042042211936</v>
       </c>
       <c r="E5">
-        <v>0.56344566969533982</v>
+        <v>0.55058126026243925</v>
       </c>
       <c r="F5">
-        <v>0.57795037557796503</v>
+        <v>0.566092663960025</v>
       </c>
       <c r="G5">
-        <v>0.58777547398849983</v>
+        <v>0.5853524597897628</v>
       </c>
       <c r="H5">
-        <v>0.5936231961867201</v>
+        <v>0.59258204217223898</v>
       </c>
       <c r="I5">
-        <v>0.55424505753119035</v>
+        <v>0.59463791471946792</v>
       </c>
       <c r="J5">
-        <v>0.54245345476367834</v>
+        <v>0.55709116359478661</v>
       </c>
       <c r="K5">
-        <v>0.50620554619299518</v>
+        <v>0.54479185302281941</v>
       </c>
       <c r="L5">
-        <v>0.49169477492986119</v>
+        <v>0.50547006483513091</v>
       </c>
       <c r="M5">
-        <v>0.4826683856076443</v>
+        <v>0.48326955392918802</v>
       </c>
       <c r="N5">
-        <v>0.5018653939740978</v>
+        <v>0.47350870992944821</v>
       </c>
       <c r="O5">
-        <v>0.50895816579200448</v>
+        <v>0.48750570506823082</v>
       </c>
       <c r="P5">
-        <v>0.5179164706440853</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.49733455022137157</v>
+      </c>
+      <c r="Q5">
+        <v>0.50688290529227542</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>0.53495841456433868</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C6">
-        <v>0.53896005085418353</v>
+        <v>0.5347893527016121</v>
       </c>
       <c r="D6">
-        <v>0.54902363334549498</v>
+        <v>0.5398206981723126</v>
       </c>
       <c r="E6">
-        <v>0.56330054605051605</v>
+        <v>0.54921163612514901</v>
       </c>
       <c r="F6">
-        <v>0.60638100973063691</v>
+        <v>0.56186104860254105</v>
       </c>
       <c r="G6">
-        <v>0.58929527734074849</v>
+        <v>0.60203581232346626</v>
       </c>
       <c r="H6">
-        <v>0.58785073504449681</v>
+        <v>0.58666698634247139</v>
       </c>
       <c r="I6">
-        <v>0.55851840578626066</v>
+        <v>0.58565744108380513</v>
       </c>
       <c r="J6">
-        <v>0.5182631785092362</v>
+        <v>0.55935946742939935</v>
       </c>
       <c r="K6">
-        <v>0.50239322982359935</v>
+        <v>0.51828516630222532</v>
       </c>
       <c r="L6">
-        <v>0.47127174441217973</v>
+        <v>0.50146033161316361</v>
       </c>
       <c r="M6">
-        <v>0.46393439964441913</v>
+        <v>0.46912773097817101</v>
       </c>
       <c r="N6">
-        <v>0.44759270852616623</v>
+        <v>0.46683341545323109</v>
       </c>
       <c r="O6">
-        <v>0.45590145197544008</v>
+        <v>0.44750584841839408</v>
       </c>
       <c r="P6">
-        <v>0.46280675906848168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.46218531285749459</v>
+      </c>
+      <c r="Q6">
+        <v>0.46955907086350868</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>0.3896371644112433</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C7">
-        <v>0.52929832848236658</v>
+        <v>0.38842870208464397</v>
       </c>
       <c r="D7">
-        <v>0.60109637080664102</v>
+        <v>0.52700567358998662</v>
       </c>
       <c r="E7">
-        <v>0.63577445345666406</v>
+        <v>0.59484477430491767</v>
       </c>
       <c r="F7">
-        <v>0.64960609119932999</v>
+        <v>0.631202268715085</v>
       </c>
       <c r="G7">
-        <v>0.65234636904364274</v>
+        <v>0.64298421528422589</v>
       </c>
       <c r="H7">
-        <v>0.64536546591670185</v>
+        <v>0.64591980599033638</v>
       </c>
       <c r="I7">
-        <v>0.65547419101604965</v>
+        <v>0.63734012535939855</v>
       </c>
       <c r="J7">
-        <v>0.63069888568919963</v>
+        <v>0.64904620820905445</v>
       </c>
       <c r="K7">
-        <v>0.59399454794747786</v>
+        <v>0.62324171688891605</v>
       </c>
       <c r="L7">
-        <v>0.56820711984902417</v>
+        <v>0.58642350236449281</v>
       </c>
       <c r="M7">
-        <v>0.53875591520645116</v>
+        <v>0.56147797991620085</v>
       </c>
       <c r="N7">
-        <v>0.51943561556306972</v>
+        <v>0.53368546673715789</v>
       </c>
       <c r="O7">
-        <v>0.52517200475261483</v>
+        <v>0.51605530604662975</v>
       </c>
       <c r="P7">
-        <v>0.54214840303187517</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52099290236469298</v>
+      </c>
+      <c r="Q7">
+        <v>0.53572553827182612</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>0.44447335877449812</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C8">
-        <v>0.51206359701151549</v>
+        <v>0.44529002228086728</v>
       </c>
       <c r="D8">
-        <v>0.5791518328432268</v>
+        <v>0.51220007273672552</v>
       </c>
       <c r="E8">
-        <v>0.59549178540332692</v>
+        <v>0.57937724934855883</v>
       </c>
       <c r="F8">
-        <v>0.60031446446823877</v>
+        <v>0.59618808127965506</v>
       </c>
       <c r="G8">
-        <v>0.60578263708112001</v>
+        <v>0.59931916018164777</v>
       </c>
       <c r="H8">
-        <v>0.62633775626872257</v>
+        <v>0.60654132697471519</v>
       </c>
       <c r="I8">
-        <v>0.60568600336097167</v>
+        <v>0.62426932648129541</v>
       </c>
       <c r="J8">
-        <v>0.5768287372113603</v>
+        <v>0.60359927341446218</v>
       </c>
       <c r="K8">
-        <v>0.52087161957079886</v>
+        <v>0.57462509319585831</v>
       </c>
       <c r="L8">
-        <v>0.47724353906958661</v>
+        <v>0.52180097178833662</v>
       </c>
       <c r="M8">
-        <v>0.4737500113507323</v>
+        <v>0.48070860250607378</v>
       </c>
       <c r="N8">
-        <v>0.49081061143591492</v>
+        <v>0.47551881667632973</v>
       </c>
       <c r="O8">
-        <v>0.51848100120049145</v>
+        <v>0.49127694923674048</v>
       </c>
       <c r="P8">
-        <v>0.50203305928603348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52070705792682204</v>
+      </c>
+      <c r="Q8">
+        <v>0.50757665427251375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>0.44642326585644648</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C9">
-        <v>0.51357213366073218</v>
+        <v>0.44625920187085177</v>
       </c>
       <c r="D9">
-        <v>0.57629771412532727</v>
+        <v>0.51321473696588105</v>
       </c>
       <c r="E9">
-        <v>0.59063100823943049</v>
+        <v>0.57820580031796931</v>
       </c>
       <c r="F9">
-        <v>0.59383523909855229</v>
+        <v>0.59146132281102992</v>
       </c>
       <c r="G9">
-        <v>0.59746634083895922</v>
+        <v>0.59621409503604272</v>
       </c>
       <c r="H9">
-        <v>0.61626446647562161</v>
+        <v>0.59711893967714347</v>
       </c>
       <c r="I9">
-        <v>0.60342156695333748</v>
+        <v>0.61735628869775239</v>
       </c>
       <c r="J9">
-        <v>0.59168356777839881</v>
+        <v>0.60065865263036389</v>
       </c>
       <c r="K9">
-        <v>0.56068217019557676</v>
+        <v>0.58791707253238112</v>
       </c>
       <c r="L9">
-        <v>0.5198657028565421</v>
+        <v>0.5617081466258339</v>
       </c>
       <c r="M9">
-        <v>0.51254622313870923</v>
+        <v>0.5207166250606774</v>
       </c>
       <c r="N9">
-        <v>0.53783395570442449</v>
+        <v>0.51663614323832574</v>
       </c>
       <c r="O9">
-        <v>0.56194901934176877</v>
+        <v>0.53616348952581916</v>
       </c>
       <c r="P9">
-        <v>0.55220777691483303</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55954513699852737</v>
+      </c>
+      <c r="Q9">
+        <v>0.54992142863847404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>0.44425336029680879</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C10">
-        <v>0.51266123172742617</v>
+        <v>0.44295369648606109</v>
       </c>
       <c r="D10">
-        <v>0.57556066528614036</v>
+        <v>0.51066726091105974</v>
       </c>
       <c r="E10">
-        <v>0.59058491592244855</v>
+        <v>0.57547784320883388</v>
       </c>
       <c r="F10">
-        <v>0.59375501662346297</v>
+        <v>0.59059661635013949</v>
       </c>
       <c r="G10">
-        <v>0.59534265318851132</v>
+        <v>0.59397909293940321</v>
       </c>
       <c r="H10">
-        <v>0.61449489286421133</v>
+        <v>0.59787172238037867</v>
       </c>
       <c r="I10">
-        <v>0.60223086560592942</v>
+        <v>0.61846680431729995</v>
       </c>
       <c r="J10">
-        <v>0.59089148468122543</v>
+        <v>0.60448028736442205</v>
       </c>
       <c r="K10">
-        <v>0.56675020370314066</v>
+        <v>0.59535076259241804</v>
       </c>
       <c r="L10">
-        <v>0.52671847447151976</v>
+        <v>0.5703853640793175</v>
       </c>
       <c r="M10">
-        <v>0.52015071734708274</v>
+        <v>0.53175375315444484</v>
       </c>
       <c r="N10">
-        <v>0.54176304002300413</v>
+        <v>0.52584627693623798</v>
       </c>
       <c r="O10">
-        <v>0.56751512808530336</v>
+        <v>0.54510172142056623</v>
       </c>
       <c r="P10">
-        <v>0.55787791287152777</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.56731455145401566</v>
+      </c>
+      <c r="Q10">
+        <v>0.55606260624628057</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>0.44647102729246918</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C11">
-        <v>0.51405817077936178</v>
+        <v>0.44629460339102661</v>
       </c>
       <c r="D11">
-        <v>0.57964941871840847</v>
+        <v>0.51259828613670544</v>
       </c>
       <c r="E11">
-        <v>0.5945887389508403</v>
+        <v>0.57951885073210785</v>
       </c>
       <c r="F11">
-        <v>0.5975106747901745</v>
+        <v>0.59354911124398269</v>
       </c>
       <c r="G11">
-        <v>0.6027202165157608</v>
+        <v>0.59929409036839631</v>
       </c>
       <c r="H11">
-        <v>0.62235129320141291</v>
+        <v>0.60287645955058466</v>
       </c>
       <c r="I11">
-        <v>0.60686821917820444</v>
+        <v>0.62043653379916242</v>
       </c>
       <c r="J11">
-        <v>0.59660089639683556</v>
+        <v>0.60522460011766743</v>
       </c>
       <c r="K11">
-        <v>0.56354113972559039</v>
+        <v>0.59400790550424076</v>
       </c>
       <c r="L11">
-        <v>0.52002513408478634</v>
+        <v>0.56399455128275722</v>
       </c>
       <c r="M11">
-        <v>0.51399697827140611</v>
+        <v>0.51828052915180889</v>
       </c>
       <c r="N11">
-        <v>0.53590984010812759</v>
+        <v>0.51060442162879882</v>
       </c>
       <c r="O11">
-        <v>0.56487789058401539</v>
+        <v>0.53003613421285345</v>
       </c>
       <c r="P11">
-        <v>0.56294248868203811</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55772196532723761</v>
+      </c>
+      <c r="Q11">
+        <v>0.5558672471472117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>0.544888307383815</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C12">
-        <v>0.55596364605424264</v>
+        <v>0.54592577156803379</v>
       </c>
       <c r="D12">
-        <v>0.58384855256802148</v>
+        <v>0.55827987312747585</v>
       </c>
       <c r="E12">
-        <v>0.60449843369791134</v>
+        <v>0.58823267466986351</v>
       </c>
       <c r="F12">
-        <v>0.61923790286899283</v>
+        <v>0.60835110432564432</v>
       </c>
       <c r="G12">
-        <v>0.62493030908607927</v>
+        <v>0.62620228229732622</v>
       </c>
       <c r="H12">
-        <v>0.62347006014016104</v>
+        <v>0.63036486673100456</v>
       </c>
       <c r="I12">
-        <v>0.60309234013237512</v>
+        <v>0.62859374153197256</v>
       </c>
       <c r="J12">
-        <v>0.57278314791195806</v>
+        <v>0.60844914343259415</v>
       </c>
       <c r="K12">
-        <v>0.52930281476304308</v>
+        <v>0.57896975304052423</v>
       </c>
       <c r="L12">
-        <v>0.48452685183045202</v>
+        <v>0.53306087830321647</v>
       </c>
       <c r="M12">
-        <v>0.45360108284432271</v>
+        <v>0.4897095395874847</v>
       </c>
       <c r="N12">
-        <v>0.4577954667290432</v>
+        <v>0.4538174526031804</v>
       </c>
       <c r="O12">
-        <v>0.45717056700330122</v>
+        <v>0.45938807798775561</v>
       </c>
       <c r="P12">
-        <v>0.44310546280847007</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.46297429439047538</v>
+      </c>
+      <c r="Q12">
+        <v>0.44460839249699358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>0.54364809507973322</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C13">
-        <v>0.55549088517911482</v>
+        <v>0.54665811340458881</v>
       </c>
       <c r="D13">
-        <v>0.57455362989028969</v>
+        <v>0.56015490443046601</v>
       </c>
       <c r="E13">
-        <v>0.58597062984883053</v>
+        <v>0.57727137142245277</v>
       </c>
       <c r="F13">
-        <v>0.59643630030502104</v>
+        <v>0.58758914411430962</v>
       </c>
       <c r="G13">
-        <v>0.59317680088735392</v>
+        <v>0.59825720656475223</v>
       </c>
       <c r="H13">
-        <v>0.59529846911702133</v>
+        <v>0.59556672708980485</v>
       </c>
       <c r="I13">
-        <v>0.57797383019251125</v>
+        <v>0.59856291629877467</v>
       </c>
       <c r="J13">
-        <v>0.56051831186706014</v>
+        <v>0.58045074629051407</v>
       </c>
       <c r="K13">
-        <v>0.51290765896449675</v>
+        <v>0.5586746096328572</v>
       </c>
       <c r="L13">
-        <v>0.49016239941024847</v>
+        <v>0.51585495783587709</v>
       </c>
       <c r="M13">
-        <v>0.47511954160912789</v>
+        <v>0.49360129239266148</v>
       </c>
       <c r="N13">
-        <v>0.45350465559853098</v>
+        <v>0.48310192926367912</v>
       </c>
       <c r="O13">
-        <v>0.42500812553536121</v>
+        <v>0.45838460159703542</v>
       </c>
       <c r="P13">
-        <v>0.38235280990988518</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.43278989614833963</v>
+      </c>
+      <c r="Q13">
+        <v>0.38895775928248888</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>0.39121505737203482</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C14">
-        <v>0.53002884804964978</v>
+        <v>0.38983530009395961</v>
       </c>
       <c r="D14">
-        <v>0.5976757825506186</v>
+        <v>0.53233527053923335</v>
       </c>
       <c r="E14">
-        <v>0.63371417217362835</v>
+        <v>0.60474298117543124</v>
       </c>
       <c r="F14">
-        <v>0.64637835501946617</v>
+        <v>0.63675806290590053</v>
       </c>
       <c r="G14">
-        <v>0.64958017878413155</v>
+        <v>0.65106514122493075</v>
       </c>
       <c r="H14">
-        <v>0.64655059522184444</v>
+        <v>0.65449040966278937</v>
       </c>
       <c r="I14">
-        <v>0.65586490151904608</v>
+        <v>0.64975869362915506</v>
       </c>
       <c r="J14">
-        <v>0.63908808265484962</v>
+        <v>0.66228218778357761</v>
       </c>
       <c r="K14">
-        <v>0.61143135419298378</v>
+        <v>0.64322670971429152</v>
       </c>
       <c r="L14">
-        <v>0.59691031526712601</v>
+        <v>0.61840207102614475</v>
       </c>
       <c r="M14">
-        <v>0.5749366555764972</v>
+        <v>0.60729241796066802</v>
       </c>
       <c r="N14">
-        <v>0.55450689893716754</v>
+        <v>0.58282160262029203</v>
       </c>
       <c r="O14">
-        <v>0.55468569947220248</v>
+        <v>0.5621682355931964</v>
       </c>
       <c r="P14">
-        <v>0.5768184440123183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55767306048298815</v>
+      </c>
+      <c r="Q14">
+        <v>0.58306207648127806</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>0.38919191682766657</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C15">
-        <v>0.52790929228276162</v>
+        <v>0.39226486966483709</v>
       </c>
       <c r="D15">
-        <v>0.59798959811719155</v>
+        <v>0.53378928511869994</v>
       </c>
       <c r="E15">
-        <v>0.63553833079384769</v>
+        <v>0.60575824080057483</v>
       </c>
       <c r="F15">
-        <v>0.64834513802606619</v>
+        <v>0.63859523262312146</v>
       </c>
       <c r="G15">
-        <v>0.6506836419068267</v>
+        <v>0.65357756465621031</v>
       </c>
       <c r="H15">
-        <v>0.64669124681532419</v>
+        <v>0.65611742639414672</v>
       </c>
       <c r="I15">
-        <v>0.65754530654444709</v>
+        <v>0.6531141880904564</v>
       </c>
       <c r="J15">
-        <v>0.64010144118842516</v>
+        <v>0.66264947897191695</v>
       </c>
       <c r="K15">
-        <v>0.61185336457811845</v>
+        <v>0.64572452893971433</v>
       </c>
       <c r="L15">
-        <v>0.59911591140413545</v>
+        <v>0.61776304476009603</v>
       </c>
       <c r="M15">
-        <v>0.57288716514585947</v>
+        <v>0.60779816648586282</v>
       </c>
       <c r="N15">
-        <v>0.55166428501925591</v>
+        <v>0.58364697517714992</v>
       </c>
       <c r="O15">
-        <v>0.55132186532445726</v>
+        <v>0.56062830368141559</v>
       </c>
       <c r="P15">
-        <v>0.5730415234831846</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55433630451375882</v>
+      </c>
+      <c r="Q15">
+        <v>0.58239190469730484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>0.39172862115266011</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C16">
-        <v>0.53202519980094864</v>
+        <v>0.392088244850472</v>
       </c>
       <c r="D16">
-        <v>0.60375935049010232</v>
+        <v>0.53103974556881872</v>
       </c>
       <c r="E16">
-        <v>0.63699104688726704</v>
+        <v>0.60265441654999696</v>
       </c>
       <c r="F16">
-        <v>0.65061316375701894</v>
+        <v>0.63509002947281379</v>
       </c>
       <c r="G16">
-        <v>0.65354260592710567</v>
+        <v>0.64922046806601341</v>
       </c>
       <c r="H16">
-        <v>0.64801066053545187</v>
+        <v>0.65241959524033144</v>
       </c>
       <c r="I16">
-        <v>0.66043162759887308</v>
+        <v>0.64905273708304367</v>
       </c>
       <c r="J16">
-        <v>0.6427124293706411</v>
+        <v>0.65942639677704618</v>
       </c>
       <c r="K16">
-        <v>0.61554093062033777</v>
+        <v>0.64217075664828516</v>
       </c>
       <c r="L16">
-        <v>0.6061968899054383</v>
+        <v>0.61484499847392038</v>
       </c>
       <c r="M16">
-        <v>0.5831073621864884</v>
+        <v>0.60388478876471485</v>
       </c>
       <c r="N16">
-        <v>0.55305057140753966</v>
+        <v>0.57920123070322316</v>
       </c>
       <c r="O16">
-        <v>0.55126226465319239</v>
+        <v>0.5582681341663347</v>
       </c>
       <c r="P16">
-        <v>0.57413429918624537</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.55558883615330923</v>
+      </c>
+      <c r="Q16">
+        <v>0.57649834582299386</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>0.39330921129609397</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C17">
-        <v>0.53171501782359853</v>
+        <v>0.39199021018277919</v>
       </c>
       <c r="D17">
-        <v>0.60075377535141694</v>
+        <v>0.53123427134859225</v>
       </c>
       <c r="E17">
-        <v>0.63499931370118412</v>
+        <v>0.60448946476511944</v>
       </c>
       <c r="F17">
-        <v>0.64687248190666746</v>
+        <v>0.63808937482053052</v>
       </c>
       <c r="G17">
-        <v>0.64970446081680089</v>
+        <v>0.65094318600420953</v>
       </c>
       <c r="H17">
-        <v>0.64514978719716642</v>
+        <v>0.65569795239546946</v>
       </c>
       <c r="I17">
-        <v>0.65538030680332693</v>
+        <v>0.65109454666552602</v>
       </c>
       <c r="J17">
-        <v>0.6397474810978625</v>
+        <v>0.66195308566114242</v>
       </c>
       <c r="K17">
-        <v>0.61290721435775264</v>
+        <v>0.64488664807102414</v>
       </c>
       <c r="L17">
-        <v>0.60229363366265776</v>
+        <v>0.61931299207179036</v>
       </c>
       <c r="M17">
-        <v>0.57579651890478012</v>
+        <v>0.60822375264206441</v>
       </c>
       <c r="N17">
-        <v>0.55400134568478554</v>
+        <v>0.58615758191952561</v>
       </c>
       <c r="O17">
-        <v>0.55342290271880779</v>
+        <v>0.56725188414567362</v>
       </c>
       <c r="P17">
-        <v>0.57537500951955778</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.56562111356763511</v>
+      </c>
+      <c r="Q17">
+        <v>0.58704539692046476</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>0.54774453309523219</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C18">
-        <v>0.55268197081298376</v>
+        <v>0.54867762236787776</v>
       </c>
       <c r="D18">
-        <v>0.57710379978609139</v>
+        <v>0.55136006068792209</v>
       </c>
       <c r="E18">
-        <v>0.5976293335095868</v>
+        <v>0.57584919461037909</v>
       </c>
       <c r="F18">
-        <v>0.62455494996884131</v>
+        <v>0.59646090309480559</v>
       </c>
       <c r="G18">
-        <v>0.62376845965962358</v>
+        <v>0.62386113970447044</v>
       </c>
       <c r="H18">
-        <v>0.6224022850797073</v>
+        <v>0.62339923234087669</v>
       </c>
       <c r="I18">
-        <v>0.59208587141895364</v>
+        <v>0.62147997733972082</v>
       </c>
       <c r="J18">
-        <v>0.59000199839209255</v>
+        <v>0.59411305090761579</v>
       </c>
       <c r="K18">
-        <v>0.55074493703473804</v>
+        <v>0.58505186973050838</v>
       </c>
       <c r="L18">
-        <v>0.52907443140730792</v>
+        <v>0.54405762067372909</v>
       </c>
       <c r="M18">
-        <v>0.52328479600082656</v>
+        <v>0.52329110028220271</v>
       </c>
       <c r="N18">
-        <v>0.53918895860469529</v>
+        <v>0.51766915959725068</v>
       </c>
       <c r="O18">
-        <v>0.54416358399559805</v>
+        <v>0.53481710569450513</v>
       </c>
       <c r="P18">
-        <v>0.54604284603472286</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.54194578603230847</v>
+      </c>
+      <c r="Q18">
+        <v>0.54983280677145963</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>0.54938040269276878</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C19">
-        <v>0.55770651248068215</v>
+        <v>0.54989018604628337</v>
       </c>
       <c r="D19">
-        <v>0.5767595371913623</v>
+        <v>0.55492560049258843</v>
       </c>
       <c r="E19">
-        <v>0.60086505553128355</v>
+        <v>0.57512069640604913</v>
       </c>
       <c r="F19">
-        <v>0.63588806448319635</v>
+        <v>0.59771718747533453</v>
       </c>
       <c r="G19">
-        <v>0.62957738167091448</v>
+        <v>0.63246530501370002</v>
       </c>
       <c r="H19">
-        <v>0.62710482355377117</v>
+        <v>0.63034418180203944</v>
       </c>
       <c r="I19">
-        <v>0.60573236023364296</v>
+        <v>0.6246940533684755</v>
       </c>
       <c r="J19">
-        <v>0.57066293798275325</v>
+        <v>0.60560322140628842</v>
       </c>
       <c r="K19">
-        <v>0.55241560817441093</v>
+        <v>0.57225948199893129</v>
       </c>
       <c r="L19">
-        <v>0.53165302338132969</v>
+        <v>0.55118298687163048</v>
       </c>
       <c r="M19">
-        <v>0.53432122764104351</v>
+        <v>0.53218443699211548</v>
       </c>
       <c r="N19">
-        <v>0.53517989731369475</v>
+        <v>0.53067254681452958</v>
       </c>
       <c r="O19">
-        <v>0.53578389267518789</v>
+        <v>0.5323428929574755</v>
       </c>
       <c r="P19">
-        <v>0.52608735752760949</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.53263716328555466</v>
+      </c>
+      <c r="Q19">
+        <v>0.52627672519718627</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>0.55161851645272342</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C20">
-        <v>0.56121951933966563</v>
+        <v>0.54691999418528559</v>
       </c>
       <c r="D20">
-        <v>0.59043185902926487</v>
+        <v>0.55471901635539089</v>
       </c>
       <c r="E20">
-        <v>0.6182238644841892</v>
+        <v>0.58199990789699607</v>
       </c>
       <c r="F20">
-        <v>0.63329859467056615</v>
+        <v>0.61213862336862335</v>
       </c>
       <c r="G20">
-        <v>0.6364522064096042</v>
+        <v>0.62669562512328225</v>
       </c>
       <c r="H20">
-        <v>0.61716295261522358</v>
+        <v>0.62803933654953781</v>
       </c>
       <c r="I20">
-        <v>0.60033438184015653</v>
+        <v>0.60949480023027836</v>
       </c>
       <c r="J20">
-        <v>0.56764985689393077</v>
+        <v>0.59451074131042636</v>
       </c>
       <c r="K20">
-        <v>0.54491840602398023</v>
+        <v>0.56170513473700745</v>
       </c>
       <c r="L20">
-        <v>0.54138121946434359</v>
+        <v>0.54283384371501509</v>
       </c>
       <c r="M20">
-        <v>0.54928035467326852</v>
+        <v>0.54082823656669254</v>
       </c>
       <c r="N20">
-        <v>0.54950817906153493</v>
+        <v>0.5553313888201612</v>
       </c>
       <c r="O20">
-        <v>0.56304577824230506</v>
+        <v>0.55548946199689686</v>
       </c>
       <c r="P20">
-        <v>0.55299831242988806</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.56914220039005226</v>
+      </c>
+      <c r="Q20">
+        <v>0.55590015605555598</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>0.46188937480225101</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C21">
-        <v>0.53845778290064483</v>
+        <v>0.46323790044473451</v>
       </c>
       <c r="D21">
-        <v>0.5390816251175734</v>
+        <v>0.5388629493074315</v>
       </c>
       <c r="E21">
-        <v>0.55357193336996358</v>
+        <v>0.53999050782267655</v>
       </c>
       <c r="F21">
-        <v>0.57621047848779372</v>
+        <v>0.56255279812354197</v>
       </c>
       <c r="G21">
-        <v>0.58142680301620131</v>
+        <v>0.57949910904467039</v>
       </c>
       <c r="H21">
-        <v>0.52479890962814812</v>
+        <v>0.58592429708670712</v>
       </c>
       <c r="I21">
-        <v>0.50472481102288025</v>
+        <v>0.52875410446094229</v>
       </c>
       <c r="J21">
-        <v>0.49961395828863919</v>
+        <v>0.50670635602187519</v>
       </c>
       <c r="K21">
-        <v>0.47320311708997459</v>
+        <v>0.4959225848612312</v>
       </c>
       <c r="L21">
-        <v>0.44735703078526978</v>
+        <v>0.47352258179260609</v>
       </c>
       <c r="M21">
-        <v>0.40168550010040871</v>
+        <v>0.4457478299774098</v>
       </c>
       <c r="N21">
-        <v>0.35624827900152711</v>
+        <v>0.40265889885031908</v>
       </c>
       <c r="O21">
-        <v>0.30589360562075268</v>
+        <v>0.35636168483852743</v>
       </c>
       <c r="P21">
-        <v>0.21656627579096141</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.30913274854515022</v>
+      </c>
+      <c r="Q21">
+        <v>0.22570478470688921</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>0.45932238408871578</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C22">
-        <v>0.53659903353612481</v>
+        <v>0.4589203090153659</v>
       </c>
       <c r="D22">
-        <v>0.53729721810495024</v>
+        <v>0.53781370298843179</v>
       </c>
       <c r="E22">
-        <v>0.55673545087154952</v>
+        <v>0.5372922391467807</v>
       </c>
       <c r="F22">
-        <v>0.58322778716839019</v>
+        <v>0.55458073512811867</v>
       </c>
       <c r="G22">
-        <v>0.59819986785524792</v>
+        <v>0.57882460576469175</v>
       </c>
       <c r="H22">
-        <v>0.54627011520115776</v>
+        <v>0.59234907600824527</v>
       </c>
       <c r="I22">
-        <v>0.53005259323685328</v>
+        <v>0.53705300006384282</v>
       </c>
       <c r="J22">
-        <v>0.50905675390739702</v>
+        <v>0.51869571829988781</v>
       </c>
       <c r="K22">
-        <v>0.49454987748119472</v>
+        <v>0.50543407157026909</v>
       </c>
       <c r="L22">
-        <v>0.46703594180615521</v>
+        <v>0.48858851719033758</v>
       </c>
       <c r="M22">
-        <v>0.41936201446128391</v>
+        <v>0.45556861234431018</v>
       </c>
       <c r="N22">
-        <v>0.39514012161741302</v>
+        <v>0.41030221811327139</v>
       </c>
       <c r="O22">
-        <v>0.34749650994076958</v>
+        <v>0.38587644927205123</v>
       </c>
       <c r="P22">
-        <v>0.26146597911932717</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.33563373209260827</v>
+      </c>
+      <c r="Q22">
+        <v>0.24822007740458399</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>0.54149717228784278</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C23">
-        <v>0.54782368459945874</v>
+        <v>0.54120237212309974</v>
       </c>
       <c r="D23">
-        <v>0.57296180479483472</v>
+        <v>0.54697118999348804</v>
       </c>
       <c r="E23">
-        <v>0.58758220476728551</v>
+        <v>0.57625482584740462</v>
       </c>
       <c r="F23">
-        <v>0.55203534781509322</v>
+        <v>0.58681187058204909</v>
       </c>
       <c r="G23">
-        <v>0.47621054910034621</v>
+        <v>0.55248644127103574</v>
       </c>
       <c r="H23">
-        <v>0.42397831781816142</v>
+        <v>0.47842869035759888</v>
       </c>
       <c r="I23">
-        <v>0.4034217162749375</v>
+        <v>0.42168389511489152</v>
       </c>
       <c r="J23">
-        <v>0.36891335977825579</v>
+        <v>0.40705728550468129</v>
       </c>
       <c r="K23">
-        <v>0.30573194760923339</v>
+        <v>0.36920994542585928</v>
       </c>
       <c r="L23">
-        <v>0.24712963696556781</v>
+        <v>0.30569229548718913</v>
       </c>
       <c r="M23">
-        <v>0.16885249144798309</v>
+        <v>0.2460486402753157</v>
       </c>
       <c r="N23">
-        <v>9.4242385258680408E-2</v>
+        <v>0.1696236646280247</v>
       </c>
       <c r="O23">
-        <v>5.7670116249768907E-2</v>
+        <v>9.4106449332160558E-2</v>
       </c>
       <c r="P23">
-        <v>-4.2180665088470633E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>5.5757111585166018E-2</v>
+      </c>
+      <c r="Q23">
+        <v>-5.252151737486728E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>0.1572613940942498</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C24">
-        <v>0.15385232300936491</v>
+        <v>0.59070870120026997</v>
       </c>
       <c r="D24">
-        <v>0.197516537230571</v>
-      </c>
-      <c r="E24">
-        <v>0.1232051377605918</v>
+        <v>0.6461399010014387</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.67366967999477179</v>
       </c>
       <c r="F24">
-        <v>-2.0352038573683558E-2</v>
+        <v>0.69450633894956193</v>
       </c>
       <c r="G24">
-        <v>-5.6729615869092623E-3</v>
+        <v>0.70164338980822916</v>
       </c>
       <c r="H24">
-        <v>-2.8527191619068019E-2</v>
+        <v>0.71114521163449262</v>
       </c>
       <c r="I24">
-        <v>-0.1229063297701673</v>
+        <v>0.71059526766886316</v>
       </c>
       <c r="J24">
-        <v>-0.20020498925667771</v>
+        <v>0.71152531230056737</v>
       </c>
       <c r="K24">
-        <v>-0.21012182048582809</v>
+        <v>0.69203454534365005</v>
       </c>
       <c r="L24">
-        <v>-0.2321798899588999</v>
+        <v>0.66274054806939764</v>
       </c>
       <c r="M24">
-        <v>-0.25031983870796148</v>
+        <v>0.63745635394320399</v>
       </c>
       <c r="N24">
-        <v>-0.34339145384528841</v>
+        <v>0.58087065699484708</v>
       </c>
       <c r="O24">
-        <v>-0.39543389885446018</v>
+        <v>0.53765109351575457</v>
       </c>
       <c r="P24">
-        <v>-0.44032109972456701</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.48341337098710552</v>
+      </c>
+      <c r="Q24">
+        <v>0.43222767184566069</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>0.12400275647408909</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C25">
-        <v>0.12318282789114</v>
+        <v>0.59142389682407048</v>
       </c>
       <c r="D25">
-        <v>0.10995885538009879</v>
+        <v>0.65099243188911537</v>
       </c>
       <c r="E25">
-        <v>9.9933973153101832E-2</v>
-      </c>
-      <c r="F25">
-        <v>6.85424342699614E-2</v>
+        <v>0.69042994455600493</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.72418367330630329</v>
       </c>
       <c r="G25">
-        <v>-4.2089416500582073E-2</v>
+        <v>0.74006480245211814</v>
       </c>
       <c r="H25">
-        <v>-9.2317197829702352E-2</v>
+        <v>0.74965684563717705</v>
       </c>
       <c r="I25">
-        <v>-0.16968842880871959</v>
+        <v>0.74754186354349761</v>
       </c>
       <c r="J25">
-        <v>-0.23114323417731761</v>
+        <v>0.73225554569222662</v>
       </c>
       <c r="K25">
-        <v>-0.31356421588109362</v>
+        <v>0.73277550902293387</v>
       </c>
       <c r="L25">
-        <v>-0.39543074182020688</v>
+        <v>0.73044511400138801</v>
       </c>
       <c r="M25">
-        <v>-0.46129051478615513</v>
+        <v>0.70390659396362376</v>
       </c>
       <c r="N25">
-        <v>-0.5164767455601027</v>
+        <v>0.67967944567352823</v>
       </c>
       <c r="O25">
-        <v>-0.56525465342779202</v>
+        <v>0.62857771582164856</v>
       </c>
       <c r="P25">
-        <v>-0.59423965961389691</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.601298088473321</v>
+      </c>
+      <c r="Q25">
+        <v>0.54397965961176664</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>0.1246805854501264</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C26">
-        <v>0.1226450791214321</v>
+        <v>0.60873186766717957</v>
       </c>
       <c r="D26">
-        <v>0.14748300608742551</v>
-      </c>
-      <c r="E26">
-        <v>0.14815126773372139</v>
+        <v>0.63508867653816925</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.67669592145549951</v>
       </c>
       <c r="F26">
-        <v>8.5285090042283546E-2</v>
+        <v>0.72223186035253539</v>
       </c>
       <c r="G26">
-        <v>4.7693490320130948E-2</v>
+        <v>0.71631628923331669</v>
       </c>
       <c r="H26">
-        <v>-5.4081872227005147E-2</v>
+        <v>0.72965870594830651</v>
       </c>
       <c r="I26">
-        <v>-8.0207867342647204E-2</v>
+        <v>0.73500671602820467</v>
       </c>
       <c r="J26">
-        <v>-2.2411250069105451E-2</v>
+        <v>0.72903542452163572</v>
       </c>
       <c r="K26">
-        <v>-1.8405870054337511E-2</v>
+        <v>0.69699348970663255</v>
       </c>
       <c r="L26">
-        <v>-5.822706966330686E-2</v>
+        <v>0.68729797772825485</v>
       </c>
       <c r="M26">
-        <v>-0.2270555384417543</v>
+        <v>0.63543454915758402</v>
       </c>
       <c r="N26">
-        <v>-0.19506224306646289</v>
+        <v>0.6172890329447841</v>
       </c>
       <c r="O26">
-        <v>-0.1737421133512321</v>
+        <v>0.57696001513280748</v>
       </c>
       <c r="P26">
-        <v>-0.19546794724020869</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.5280082363423888</v>
+      </c>
+      <c r="Q26">
+        <v>0.47702755362482868</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>9.5180261810104361E-2</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C27">
-        <v>9.9821553562636972E-2</v>
+        <v>0.60887705313898699</v>
       </c>
       <c r="D27">
-        <v>8.1366152933751615E-2</v>
+        <v>0.63569209359048917</v>
       </c>
       <c r="E27">
-        <v>0.14790470067845851</v>
-      </c>
-      <c r="F27">
-        <v>7.3624353432193632E-2</v>
+        <v>0.67506117884139061</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.72312916410613159</v>
       </c>
       <c r="G27">
-        <v>3.06894440015094E-2</v>
+        <v>0.71504947408333552</v>
       </c>
       <c r="H27">
-        <v>7.45046389418553E-2</v>
+        <v>0.73028362005754321</v>
       </c>
       <c r="I27">
-        <v>8.8727837945797982E-3</v>
+        <v>0.73423157585713339</v>
       </c>
       <c r="J27">
-        <v>-5.2243635400392792E-2</v>
+        <v>0.72999158363388661</v>
       </c>
       <c r="K27">
-        <v>-0.10911484654094961</v>
+        <v>0.70221041493962866</v>
       </c>
       <c r="L27">
-        <v>-0.192515438572926</v>
+        <v>0.68742241895493228</v>
       </c>
       <c r="M27">
-        <v>-0.25440489808122629</v>
+        <v>0.64575216220557341</v>
       </c>
       <c r="N27">
-        <v>-0.16409656933164329</v>
+        <v>0.60761730453420049</v>
       </c>
       <c r="O27">
-        <v>-0.23945539531625681</v>
+        <v>0.59259912877106857</v>
       </c>
       <c r="P27">
-        <v>-0.27988375220841988</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.59496331337390795</v>
+      </c>
+      <c r="Q27">
+        <v>0.55194207341250856</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>0.59313522033428312</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C28">
-        <v>0.64880465785663344</v>
+        <v>0.5906966461744052</v>
       </c>
       <c r="D28">
-        <v>0.67567237756828757</v>
+        <v>0.65044304984733148</v>
       </c>
       <c r="E28">
-        <v>0.69498328176617197</v>
-      </c>
-      <c r="F28">
-        <v>0.70137921139489268</v>
+        <v>0.69028993909114345</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.72321788739551707</v>
       </c>
       <c r="G28">
-        <v>0.71432771919634908</v>
+        <v>0.73923339837570601</v>
       </c>
       <c r="H28">
-        <v>0.71159798920426454</v>
+        <v>0.74959940732852159</v>
       </c>
       <c r="I28">
-        <v>0.71354461201667141</v>
+        <v>0.74734693629747795</v>
       </c>
       <c r="J28">
-        <v>0.69351329506983717</v>
+        <v>0.73439887566052109</v>
       </c>
       <c r="K28">
-        <v>0.66310467431983278</v>
+        <v>0.7351460331805556</v>
       </c>
       <c r="L28">
-        <v>0.63882722628253186</v>
+        <v>0.73606667222405597</v>
       </c>
       <c r="M28">
-        <v>0.58313616316857542</v>
+        <v>0.71595611441788698</v>
       </c>
       <c r="N28">
-        <v>0.53995898382890983</v>
+        <v>0.69216275353139445</v>
       </c>
       <c r="O28">
-        <v>0.4859896352453999</v>
+        <v>0.67185420081477731</v>
       </c>
       <c r="P28">
-        <v>0.43513700135631922</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.65325159606028094</v>
+      </c>
+      <c r="Q28">
+        <v>0.61979376979007239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>0.59257572328154251</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C29">
-        <v>0.65193831123238888</v>
+        <v>0.59136632947021461</v>
       </c>
       <c r="D29">
-        <v>0.69180458046169502</v>
+        <v>0.65156660427894242</v>
       </c>
       <c r="E29">
-        <v>0.72536259350390997</v>
-      </c>
-      <c r="F29">
-        <v>0.73995638961877885</v>
+        <v>0.69194484334299156</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.72468657196156316</v>
       </c>
       <c r="G29">
-        <v>0.75230192547012054</v>
+        <v>0.74046916649677041</v>
       </c>
       <c r="H29">
-        <v>0.74719104746892595</v>
+        <v>0.75239172164949464</v>
       </c>
       <c r="I29">
-        <v>0.73510706951976779</v>
+        <v>0.74695911575026919</v>
       </c>
       <c r="J29">
-        <v>0.73484833955454898</v>
+        <v>0.73470898219009229</v>
       </c>
       <c r="K29">
-        <v>0.73383887174343754</v>
+        <v>0.73644004469197755</v>
       </c>
       <c r="L29">
-        <v>0.70528363841515818</v>
+        <v>0.73704332290370012</v>
       </c>
       <c r="M29">
-        <v>0.68416596371520877</v>
+        <v>0.71832202799965816</v>
       </c>
       <c r="N29">
-        <v>0.6311926607435171</v>
+        <v>0.69727788762806331</v>
       </c>
       <c r="O29">
-        <v>0.60353647172921954</v>
+        <v>0.67553486727119683</v>
       </c>
       <c r="P29">
-        <v>0.54544336956325878</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.65724208765197734</v>
+      </c>
+      <c r="Q29">
+        <v>0.62681484186275094</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>0.60862599395781269</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C30">
-        <v>0.63491756174546421</v>
+        <v>0.59282623480217178</v>
       </c>
       <c r="D30">
-        <v>0.67287996680631024</v>
+        <v>0.65327642283973208</v>
       </c>
       <c r="E30">
-        <v>0.71737831922085549</v>
-      </c>
-      <c r="F30">
-        <v>0.71034257059492012</v>
+        <v>0.69447472760804441</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.727421052969356</v>
       </c>
       <c r="G30">
-        <v>0.72418419498327002</v>
+        <v>0.7435512339128868</v>
       </c>
       <c r="H30">
-        <v>0.72944069578889903</v>
+        <v>0.75342605339288771</v>
       </c>
       <c r="I30">
-        <v>0.7234035390873832</v>
+        <v>0.74951128700629477</v>
       </c>
       <c r="J30">
-        <v>0.69033803329728483</v>
+        <v>0.73969560362676712</v>
       </c>
       <c r="K30">
-        <v>0.68172576927092177</v>
+        <v>0.74222410470510813</v>
       </c>
       <c r="L30">
-        <v>0.6310876687395629</v>
+        <v>0.74483864803109567</v>
       </c>
       <c r="M30">
-        <v>0.60926430850608038</v>
+        <v>0.7306444277338392</v>
       </c>
       <c r="N30">
-        <v>0.57058176930238824</v>
+        <v>0.71219156559751096</v>
       </c>
       <c r="O30">
-        <v>0.51871863392301643</v>
+        <v>0.69260230912162413</v>
       </c>
       <c r="P30">
-        <v>0.46640388830674528</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.6766829284060687</v>
+      </c>
+      <c r="Q30">
+        <v>0.65223377887527678</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>0.61188143262488759</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C31">
-        <v>0.63809343964402876</v>
+        <v>0.58947179280334472</v>
       </c>
       <c r="D31">
-        <v>0.67694175536445467</v>
+        <v>0.651237743904448</v>
       </c>
       <c r="E31">
-        <v>0.72169966713311517</v>
-      </c>
-      <c r="F31">
-        <v>0.7143599073049639</v>
+        <v>0.69243410989887078</v>
+      </c>
+      <c r="F31" s="2">
+        <v>0.72439217815161672</v>
       </c>
       <c r="G31">
-        <v>0.7267321244666235</v>
+        <v>0.73995105752890611</v>
       </c>
       <c r="H31">
-        <v>0.73017504001063904</v>
+        <v>0.75147195210390993</v>
       </c>
       <c r="I31">
-        <v>0.72524050912956761</v>
+        <v>0.74822846177884583</v>
       </c>
       <c r="J31">
-        <v>0.69537765460765832</v>
+        <v>0.73513605659520398</v>
       </c>
       <c r="K31">
-        <v>0.67854487649791284</v>
+        <v>0.73812155556185888</v>
       </c>
       <c r="L31">
-        <v>0.63519051517203273</v>
+        <v>0.74080106458733419</v>
       </c>
       <c r="M31">
-        <v>0.59157126305181251</v>
+        <v>0.72671495099954087</v>
       </c>
       <c r="N31">
-        <v>0.5763696551406513</v>
+        <v>0.7105895423537083</v>
       </c>
       <c r="O31">
-        <v>0.5785505680187476</v>
+        <v>0.69119782498065085</v>
       </c>
       <c r="P31">
-        <v>0.52934510444725313</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.67437126778781842</v>
+      </c>
+      <c r="Q31">
+        <v>0.65669082392542599</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>0.59262152965620007</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C32">
-        <v>0.6535031538811602</v>
+        <v>0.59050171288704889</v>
       </c>
       <c r="D32">
-        <v>0.69221233317520525</v>
+        <v>0.65154833997379547</v>
       </c>
       <c r="E32">
-        <v>0.72458032494509894</v>
-      </c>
-      <c r="F32">
-        <v>0.74051821162166243</v>
+        <v>0.69187754840409033</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.72489130898173282</v>
       </c>
       <c r="G32">
-        <v>0.75170765379993199</v>
+        <v>0.73941073481007835</v>
       </c>
       <c r="H32">
-        <v>0.74815044226394767</v>
+        <v>0.75116264993476722</v>
       </c>
       <c r="I32">
-        <v>0.73769501146010341</v>
+        <v>0.74561944255340706</v>
       </c>
       <c r="J32">
-        <v>0.73719424430801528</v>
+        <v>0.73232037335712863</v>
       </c>
       <c r="K32">
-        <v>0.73894953852900602</v>
+        <v>0.73458242461515788</v>
       </c>
       <c r="L32">
-        <v>0.72122736409094657</v>
+        <v>0.73658673402355246</v>
       </c>
       <c r="M32">
-        <v>0.69762409428989303</v>
+        <v>0.71100777171190643</v>
       </c>
       <c r="N32">
-        <v>0.6781064763378547</v>
+        <v>0.68816969145308182</v>
       </c>
       <c r="O32">
-        <v>0.65866767118105785</v>
+        <v>0.66931783936162415</v>
       </c>
       <c r="P32">
-        <v>0.62406628162429689</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.65392469463344349</v>
+      </c>
+      <c r="Q32">
+        <v>0.6088750120094798</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>0.58937610734359502</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C33">
-        <v>0.64974312072072482</v>
+        <v>0.59231481272800046</v>
       </c>
       <c r="D33">
-        <v>0.69067801335668544</v>
+        <v>0.65175657900450157</v>
       </c>
       <c r="E33">
-        <v>0.72375545086396242</v>
-      </c>
-      <c r="F33">
-        <v>0.74118068123115932</v>
+        <v>0.69315309634626998</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.72604347418071336</v>
       </c>
       <c r="G33">
-        <v>0.75226197946566997</v>
+        <v>0.7423286915313827</v>
       </c>
       <c r="H33">
-        <v>0.74833604665072051</v>
+        <v>0.75335599906357453</v>
       </c>
       <c r="I33">
-        <v>0.73492898320358813</v>
+        <v>0.74818941007108386</v>
       </c>
       <c r="J33">
-        <v>0.73425129196868022</v>
+        <v>0.73545737705135239</v>
       </c>
       <c r="K33">
-        <v>0.73581715039628015</v>
+        <v>0.73692060761934675</v>
       </c>
       <c r="L33">
-        <v>0.71877571699212872</v>
+        <v>0.73780843256762962</v>
       </c>
       <c r="M33">
-        <v>0.69513127661321672</v>
+        <v>0.71548859678683985</v>
       </c>
       <c r="N33">
-        <v>0.67198095529531432</v>
+        <v>0.69374729515697053</v>
       </c>
       <c r="O33">
-        <v>0.65145323749595319</v>
+        <v>0.67314673672078751</v>
       </c>
       <c r="P33">
-        <v>0.61992481902097107</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.65893049495333</v>
+      </c>
+      <c r="Q33">
+        <v>0.62084260890023557</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>0.59293858799997234</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C34">
-        <v>0.65362391698121636</v>
+        <v>0.59362603938431435</v>
       </c>
       <c r="D34">
-        <v>0.69407791891432358</v>
+        <v>0.65537675944644991</v>
       </c>
       <c r="E34">
-        <v>0.72641690420086291</v>
-      </c>
-      <c r="F34">
-        <v>0.74169601364162563</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0.75338897292178797</v>
+        <v>0.69601110594401316</v>
+      </c>
+      <c r="F34" s="2">
+        <v>0.72900997180897464</v>
+      </c>
+      <c r="G34">
+        <v>0.74443515218713407</v>
       </c>
       <c r="H34">
-        <v>0.7499027449972222</v>
+        <v>0.75536465094378791</v>
       </c>
       <c r="I34">
-        <v>0.73689914347873231</v>
+        <v>0.75218986014733302</v>
       </c>
       <c r="J34">
-        <v>0.73745628629903603</v>
+        <v>0.7392917406054329</v>
       </c>
       <c r="K34">
-        <v>0.73994204105339789</v>
+        <v>0.73992491686660911</v>
       </c>
       <c r="L34">
-        <v>0.72430669677464665</v>
+        <v>0.74102884164079774</v>
       </c>
       <c r="M34">
-        <v>0.70381141299301853</v>
+        <v>0.72162766620439811</v>
       </c>
       <c r="N34">
-        <v>0.68330030779954876</v>
+        <v>0.69624916501137202</v>
       </c>
       <c r="O34">
-        <v>0.66603733444598712</v>
+        <v>0.67339598456460703</v>
       </c>
       <c r="P34">
-        <v>0.64190880165220243</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.66011212902801442</v>
+      </c>
+      <c r="Q34">
+        <v>0.62734100036343077</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>0.59036539440360902</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C35">
-        <v>0.65130715278886298</v>
+        <v>0.59267219043288066</v>
       </c>
       <c r="D35">
-        <v>0.69173179424417486</v>
+        <v>0.65136174244261202</v>
       </c>
       <c r="E35">
-        <v>0.72621375053040427</v>
-      </c>
-      <c r="F35">
-        <v>0.74268600979494226</v>
+        <v>0.69200328598813576</v>
+      </c>
+      <c r="F35" s="2">
+        <v>0.72619279089975763</v>
       </c>
       <c r="G35">
-        <v>0.75250545038438288</v>
+        <v>0.74158093598556463</v>
       </c>
       <c r="H35">
-        <v>0.74988818261144408</v>
+        <v>0.75127274988852377</v>
       </c>
       <c r="I35">
-        <v>0.73632277718311401</v>
+        <v>0.74796307677379748</v>
       </c>
       <c r="J35">
-        <v>0.73730191547436263</v>
+        <v>0.73679392085062112</v>
       </c>
       <c r="K35">
-        <v>0.74083316203307792</v>
+        <v>0.73887512552765389</v>
       </c>
       <c r="L35">
-        <v>0.72705590888861971</v>
+        <v>0.7387018587150419</v>
       </c>
       <c r="M35">
-        <v>0.7111487224791867</v>
+        <v>0.71897954785280371</v>
       </c>
       <c r="N35">
-        <v>0.69080428427540841</v>
+        <v>0.69485426907186221</v>
       </c>
       <c r="O35">
-        <v>0.67457196049073398</v>
+        <v>0.67129260775832122</v>
       </c>
       <c r="P35">
-        <v>0.65723411733546899</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.65586808445978528</v>
+      </c>
+      <c r="Q35">
+        <v>0.62742463136973659</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>0.59109020746244578</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C36">
-        <v>0.65218430090807245</v>
+        <v>0.58996300161130433</v>
       </c>
       <c r="D36">
-        <v>0.69361718652333371</v>
+        <v>0.65035488561703059</v>
       </c>
       <c r="E36">
-        <v>0.72632487742208618</v>
-      </c>
-      <c r="F36">
-        <v>0.74174103239915146</v>
+        <v>0.69145762109833242</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.72590136136467043</v>
       </c>
       <c r="G36">
-        <v>0.75310450128759598</v>
+        <v>0.74393719582569273</v>
       </c>
       <c r="H36">
-        <v>0.74882456992809088</v>
+        <v>0.75611704899286392</v>
       </c>
       <c r="I36">
-        <v>0.73634838080178033</v>
+        <v>0.75256121227318995</v>
       </c>
       <c r="J36">
-        <v>0.73672622833141621</v>
+        <v>0.74215362580554445</v>
       </c>
       <c r="K36">
-        <v>0.73941698757708085</v>
+        <v>0.74232957274019007</v>
       </c>
       <c r="L36">
-        <v>0.71533707442268502</v>
+        <v>0.74529555242967616</v>
       </c>
       <c r="M36">
-        <v>0.69077366694757791</v>
+        <v>0.73131853668013536</v>
       </c>
       <c r="N36">
-        <v>0.66892818842123991</v>
+        <v>0.71526127979878518</v>
       </c>
       <c r="O36">
-        <v>0.65439368777576978</v>
+        <v>0.69493084268381833</v>
       </c>
       <c r="P36">
-        <v>0.60898889436723924</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.67864572211397489</v>
+      </c>
+      <c r="Q36">
+        <v>0.65927237366609515</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>0.5902903560304944</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C37">
-        <v>0.65092402088319157</v>
-      </c>
-      <c r="D37">
-        <v>0.69289434413833639</v>
+        <v>0.60591486624321722</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.65379379674798765</v>
       </c>
       <c r="E37">
-        <v>0.7253988256627486</v>
+        <v>0.70331372985757401</v>
       </c>
       <c r="F37">
-        <v>0.74137723038407966</v>
+        <v>0.71521990190527884</v>
       </c>
       <c r="G37">
-        <v>0.75090180258547046</v>
+        <v>0.6802624104092001</v>
       </c>
       <c r="H37">
-        <v>0.74754150617032389</v>
+        <v>0.67178392716272528</v>
       </c>
       <c r="I37">
-        <v>0.73588842853450465</v>
+        <v>0.68925807683254603</v>
       </c>
       <c r="J37">
-        <v>0.73718994597894416</v>
+        <v>0.6779374247188944</v>
       </c>
       <c r="K37">
-        <v>0.73766876633360534</v>
+        <v>0.63803155159093217</v>
       </c>
       <c r="L37">
-        <v>0.71549995693766677</v>
+        <v>0.59673077798189</v>
       </c>
       <c r="M37">
-        <v>0.69012792559875247</v>
+        <v>0.57034327899296</v>
       </c>
       <c r="N37">
-        <v>0.66928581607116666</v>
+        <v>0.54282930697315235</v>
       </c>
       <c r="O37">
-        <v>0.6543102293877554</v>
+        <v>0.51861908351996977</v>
       </c>
       <c r="P37">
-        <v>0.61715834035594552</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.48841011422919089</v>
+      </c>
+      <c r="Q37">
+        <v>0.46970698483274592</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>0.59201721953798714</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C38">
-        <v>0.65214751678702765</v>
+        <v>0.60855127917714269</v>
       </c>
       <c r="D38">
-        <v>0.69195182808299527</v>
-      </c>
-      <c r="E38">
-        <v>0.72530423642255593</v>
+        <v>0.66637833437668359</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.71171942234157082</v>
       </c>
       <c r="F38">
-        <v>0.74125991483924158</v>
+        <v>0.71982419854324176</v>
       </c>
       <c r="G38">
-        <v>0.75268572556421243</v>
+        <v>0.70303919156884531</v>
       </c>
       <c r="H38">
-        <v>0.74884841717439532</v>
+        <v>0.69248788066762501</v>
       </c>
       <c r="I38">
-        <v>0.73491993573501879</v>
+        <v>0.72350787713775111</v>
       </c>
       <c r="J38">
-        <v>0.73744495169116675</v>
+        <v>0.69739372942252376</v>
       </c>
       <c r="K38">
-        <v>0.73922590032833191</v>
+        <v>0.66852616919690555</v>
       </c>
       <c r="L38">
-        <v>0.71605147133153246</v>
+        <v>0.64480499623806231</v>
       </c>
       <c r="M38">
-        <v>0.69107786791295422</v>
+        <v>0.63616632777812843</v>
       </c>
       <c r="N38">
-        <v>0.66825639127235059</v>
+        <v>0.6063579227769369</v>
       </c>
       <c r="O38">
-        <v>0.65446851070547518</v>
+        <v>0.57002375922823723</v>
       </c>
       <c r="P38">
-        <v>0.62431761291040988</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52942159407226352</v>
+      </c>
+      <c r="Q38">
+        <v>0.49372986813891478</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>0.5900468185731198</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C39">
-        <v>0.65024806090803111</v>
+        <v>0.6083116473096517</v>
       </c>
       <c r="D39">
-        <v>0.69091776372434843</v>
-      </c>
-      <c r="E39">
-        <v>0.72438865204830505</v>
+        <v>0.66439023212439907</v>
+      </c>
+      <c r="E39" s="4">
+        <v>0.71212123742144207</v>
       </c>
       <c r="F39">
-        <v>0.74001281516069151</v>
+        <v>0.71896251075905304</v>
       </c>
       <c r="G39">
-        <v>0.75071586355011855</v>
+        <v>0.70449944586123847</v>
       </c>
       <c r="H39">
-        <v>0.74771989948510897</v>
+        <v>0.69397755724236576</v>
       </c>
       <c r="I39">
-        <v>0.73460379761991834</v>
+        <v>0.7160800015431581</v>
       </c>
       <c r="J39">
-        <v>0.73601011663046101</v>
+        <v>0.68683283082294255</v>
       </c>
       <c r="K39">
-        <v>0.73531920596290767</v>
+        <v>0.65567845341617981</v>
       </c>
       <c r="L39">
-        <v>0.71612164559309521</v>
+        <v>0.61756922916494428</v>
       </c>
       <c r="M39">
-        <v>0.69149498800398868</v>
+        <v>0.59566203204725032</v>
       </c>
       <c r="N39">
-        <v>0.66631981975774113</v>
+        <v>0.57014601376209106</v>
       </c>
       <c r="O39">
-        <v>0.65366988880870736</v>
+        <v>0.55208160446732013</v>
       </c>
       <c r="P39">
-        <v>0.62850815039325014</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.52666476574221588</v>
+      </c>
+      <c r="Q39">
+        <v>0.48696637413936428</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>0.58852099876764974</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C40">
-        <v>0.64996419222802138</v>
+        <v>0.56393595798497698</v>
       </c>
       <c r="D40">
-        <v>0.69064283906016555</v>
+        <v>0.57100856029021907</v>
       </c>
       <c r="E40">
-        <v>0.72399851595993769</v>
+        <v>0.5969524382576249</v>
       </c>
       <c r="F40">
-        <v>0.74173653330213407</v>
+        <v>0.63745493423033872</v>
       </c>
       <c r="G40">
-        <v>0.75179451982621248</v>
+        <v>0.67421641971643587</v>
       </c>
       <c r="H40">
-        <v>0.74786833380910189</v>
+        <v>0.66843696430770771</v>
       </c>
       <c r="I40">
-        <v>0.73521771825408022</v>
+        <v>0.62998201507570328</v>
       </c>
       <c r="J40">
-        <v>0.73619589398207941</v>
+        <v>0.6121413590158854</v>
       </c>
       <c r="K40">
-        <v>0.73994403404105069</v>
+        <v>0.58670021656458182</v>
       </c>
       <c r="L40">
-        <v>0.72363344072959601</v>
+        <v>0.5470592635666427</v>
       </c>
       <c r="M40">
-        <v>0.70730843918364483</v>
+        <v>0.48400395515360228</v>
       </c>
       <c r="N40">
-        <v>0.68498687386611778</v>
+        <v>0.39959753207724219</v>
       </c>
       <c r="O40">
-        <v>0.66624375086015508</v>
+        <v>0.34035609837807179</v>
       </c>
       <c r="P40">
-        <v>0.64725607718035139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.270417479056062</v>
+      </c>
+      <c r="Q40">
+        <v>0.20374146854996791</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>0.6060880608857403</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C41">
-        <v>0.6528924197084458</v>
+        <v>0.54063596037921291</v>
       </c>
       <c r="D41">
-        <v>0.70117643814651698</v>
+        <v>0.57432567473558482</v>
       </c>
       <c r="E41">
-        <v>0.71421823539135443</v>
+        <v>0.53575007574970457</v>
       </c>
       <c r="F41">
-        <v>0.67855695319687603</v>
+        <v>0.4879757366299734</v>
       </c>
       <c r="G41">
-        <v>0.6722499449143684</v>
+        <v>0.44447390277269261</v>
       </c>
       <c r="H41">
-        <v>0.68668735603880526</v>
+        <v>0.4542659182142435</v>
       </c>
       <c r="I41">
-        <v>0.67280706112503086</v>
+        <v>0.47754919965308168</v>
       </c>
       <c r="J41">
-        <v>0.63443584844332301</v>
+        <v>0.49415479200374651</v>
       </c>
       <c r="K41">
-        <v>0.59373876468989151</v>
+        <v>0.49349262460208843</v>
       </c>
       <c r="L41">
-        <v>0.56583758598834932</v>
+        <v>0.45769760701323708</v>
       </c>
       <c r="M41">
-        <v>0.53584076192826513</v>
+        <v>0.39399673354279902</v>
       </c>
       <c r="N41">
-        <v>0.51153040408815487</v>
+        <v>0.35069335665152102</v>
       </c>
       <c r="O41">
-        <v>0.48050670357931707</v>
+        <v>0.31799371950888988</v>
       </c>
       <c r="P41">
-        <v>0.45976640885426551</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.28438230940226872</v>
+      </c>
+      <c r="Q41">
+        <v>0.27954698998619049</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>0.6077631801714084</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C42">
-        <v>0.66327233803242769</v>
+        <v>0.47205506997270907</v>
       </c>
       <c r="D42">
-        <v>0.7108558420118547</v>
+        <v>0.56104630009235301</v>
       </c>
       <c r="E42">
-        <v>0.71916424964667514</v>
+        <v>0.54598837441701675</v>
       </c>
       <c r="F42">
-        <v>0.69940825918322802</v>
+        <v>0.54374287777435337</v>
       </c>
       <c r="G42">
-        <v>0.68662577678677517</v>
+        <v>0.56337530875283082</v>
       </c>
       <c r="H42">
-        <v>0.71915387449572377</v>
+        <v>0.57678394694312207</v>
       </c>
       <c r="I42">
-        <v>0.69276287257961466</v>
+        <v>0.59050121905463493</v>
       </c>
       <c r="J42">
-        <v>0.66340956173334209</v>
+        <v>0.55281423381299344</v>
       </c>
       <c r="K42">
-        <v>0.63594395582118857</v>
+        <v>0.51573870358523932</v>
       </c>
       <c r="L42">
-        <v>0.63012079012990407</v>
+        <v>0.45924701451021682</v>
       </c>
       <c r="M42">
-        <v>0.59764567880311392</v>
+        <v>0.43889391357083563</v>
       </c>
       <c r="N42">
-        <v>0.56183122815824726</v>
+        <v>0.42494906641467028</v>
       </c>
       <c r="O42">
-        <v>0.52098578037079468</v>
+        <v>0.40435058692376802</v>
       </c>
       <c r="P42">
-        <v>0.48738788477956441</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>0.38860515349866842</v>
+      </c>
+      <c r="Q42">
+        <v>0.37335375574730412</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>0.60923609799184164</v>
+        <v>-1.8778932657874E-2</v>
       </c>
       <c r="C43">
-        <v>0.66270454750492302</v>
+        <v>0.57005787148078391</v>
       </c>
       <c r="D43">
-        <v>0.71305964440221603</v>
+        <v>0.54782119135919427</v>
       </c>
       <c r="E43">
-        <v>0.72081864831088616</v>
+        <v>0.53522818728920019</v>
       </c>
       <c r="F43">
-        <v>0.70865049837497618</v>
+        <v>0.51772578344236908</v>
       </c>
       <c r="G43">
-        <v>0.69847230417263195</v>
+        <v>0.47984857774271389</v>
       </c>
       <c r="H43">
-        <v>0.72023150023856586</v>
+        <v>0.48382501350953888</v>
       </c>
       <c r="I43">
-        <v>0.69091705788027902</v>
+        <v>0.55043506934487052</v>
       </c>
       <c r="J43">
-        <v>0.66137266878870016</v>
+        <v>0.57309499996906565</v>
       </c>
       <c r="K43">
-        <v>0.62339888479838235</v>
+        <v>0.5648441427912807</v>
       </c>
       <c r="L43">
-        <v>0.59993154621155365</v>
+        <v>0.50389385178667634</v>
       </c>
       <c r="M43">
-        <v>0.57560312091619237</v>
+        <v>0.48062644081903139</v>
       </c>
       <c r="N43">
-        <v>0.5526491489752775</v>
+        <v>0.47362619953217022</v>
       </c>
       <c r="O43">
-        <v>0.52990851104264158</v>
+        <v>0.46243447931777393</v>
       </c>
       <c r="P43">
-        <v>0.49629006730160963</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>58</v>
-      </c>
-      <c r="B44">
-        <v>0.56315109788211293</v>
-      </c>
-      <c r="C44">
-        <v>0.56934143827455808</v>
-      </c>
-      <c r="D44">
-        <v>0.594927550919086</v>
-      </c>
-      <c r="E44">
-        <v>0.63452161256100448</v>
-      </c>
-      <c r="F44">
-        <v>0.66570247621946999</v>
-      </c>
-      <c r="G44">
-        <v>0.66124386089635667</v>
-      </c>
-      <c r="H44">
-        <v>0.61638752795823504</v>
-      </c>
-      <c r="I44">
-        <v>0.60016789995323838</v>
-      </c>
-      <c r="J44">
-        <v>0.57590043461652363</v>
-      </c>
-      <c r="K44">
-        <v>0.53715322836657875</v>
-      </c>
-      <c r="L44">
-        <v>0.47144865229771449</v>
-      </c>
-      <c r="M44">
-        <v>0.38826944086058751</v>
-      </c>
-      <c r="N44">
-        <v>0.33734682283481621</v>
-      </c>
-      <c r="O44">
-        <v>0.27505440327184799</v>
-      </c>
-      <c r="P44">
-        <v>0.2200302475341987</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45">
-        <v>0.54054859955997736</v>
-      </c>
-      <c r="C45">
-        <v>0.57403600668080912</v>
-      </c>
-      <c r="D45">
-        <v>0.53448023177434212</v>
-      </c>
-      <c r="E45">
-        <v>0.48637560373970212</v>
-      </c>
-      <c r="F45">
-        <v>0.43811776114100232</v>
-      </c>
-      <c r="G45">
-        <v>0.44935390498162042</v>
-      </c>
-      <c r="H45">
-        <v>0.47421091389960363</v>
-      </c>
-      <c r="I45">
-        <v>0.48934373441591811</v>
-      </c>
-      <c r="J45">
-        <v>0.4884538645384735</v>
-      </c>
-      <c r="K45">
-        <v>0.45002398085091261</v>
-      </c>
-      <c r="L45">
-        <v>0.38515667235526091</v>
-      </c>
-      <c r="M45">
-        <v>0.34146827981678263</v>
-      </c>
-      <c r="N45">
-        <v>0.31065011200774661</v>
-      </c>
-      <c r="O45">
-        <v>0.28344545438211838</v>
-      </c>
-      <c r="P45">
-        <v>0.27995672918333542</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>60</v>
-      </c>
-      <c r="B46">
-        <v>0.47073214600319963</v>
-      </c>
-      <c r="C46">
-        <v>0.56221601155318734</v>
-      </c>
-      <c r="D46">
-        <v>0.5441428940082419</v>
-      </c>
-      <c r="E46">
-        <v>0.54326492345690081</v>
-      </c>
-      <c r="F46">
-        <v>0.56019332247522213</v>
-      </c>
-      <c r="G46">
-        <v>0.57505961809934658</v>
-      </c>
-      <c r="H46">
-        <v>0.58825409077210478</v>
-      </c>
-      <c r="I46">
-        <v>0.55144163803676283</v>
-      </c>
-      <c r="J46">
-        <v>0.5131031642659386</v>
-      </c>
-      <c r="K46">
-        <v>0.45670291817971442</v>
-      </c>
-      <c r="L46">
-        <v>0.43111836689469779</v>
-      </c>
-      <c r="M46">
-        <v>0.42004897082341169</v>
-      </c>
-      <c r="N46">
-        <v>0.3976283200033488</v>
-      </c>
-      <c r="O46">
-        <v>0.38094996472204939</v>
-      </c>
-      <c r="P46">
-        <v>0.35956109697199268</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47">
-        <v>0.570152161653395</v>
-      </c>
-      <c r="C47">
-        <v>0.55100067019405075</v>
-      </c>
-      <c r="D47">
-        <v>0.54118555713092786</v>
-      </c>
-      <c r="E47">
-        <v>0.52614596477494113</v>
-      </c>
-      <c r="F47">
-        <v>0.49439894966009529</v>
-      </c>
-      <c r="G47">
-        <v>0.49929310668981591</v>
-      </c>
-      <c r="H47">
-        <v>0.56083753932809011</v>
-      </c>
-      <c r="I47">
-        <v>0.58045149577211119</v>
-      </c>
-      <c r="J47">
-        <v>0.57410545269509616</v>
-      </c>
-      <c r="K47">
-        <v>0.52091863973383157</v>
-      </c>
-      <c r="L47">
-        <v>0.49619897521231621</v>
-      </c>
-      <c r="M47">
-        <v>0.48584477385452812</v>
-      </c>
-      <c r="N47">
-        <v>0.47943004477289852</v>
-      </c>
-      <c r="O47">
-        <v>0.48412376704928178</v>
-      </c>
-      <c r="P47">
-        <v>0.48498656668398921</v>
+        <v>0.47324672500244541</v>
+      </c>
+      <c r="Q43">
+        <v>0.47687073242301659</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P33 B35:P47 B34:F34 H34:P34">
+  <conditionalFormatting sqref="C2:Q43">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2972,9 +2894,19 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="top10" dxfId="1" priority="1" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:Q43">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>